--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487057_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487057_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.2895</v>
+        <v>8.0581</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1014</v>
+        <v>5.6195</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1881</v>
+        <v>2.4386</v>
       </c>
       <c r="G2" t="n">
         <v>4.1924</v>
@@ -610,13 +610,13 @@
         <v>2.1231</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2395</v>
+        <v>3.0081</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1496</v>
+        <v>1.6677</v>
       </c>
       <c r="U2" t="n">
-        <v>2.09</v>
+        <v>1.3404</v>
       </c>
       <c r="V2" t="n">
         <v>0.8576</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. TAPÉ</t>
+          <t>M. LINDE GIL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6444</v>
+        <v>6.8486</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2263</v>
+        <v>6.8218</v>
       </c>
       <c r="F3" t="n">
-        <v>0.418</v>
+        <v>0.0268</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5575</v>
+        <v>6.1398</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2912</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2663</v>
+        <v>5.5023</v>
       </c>
       <c r="J3" t="n">
-        <v>4.29</v>
+        <v>7.0402</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2715</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0185</v>
+        <v>6.202</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2675</v>
+        <v>-0.9004</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0198</v>
+        <v>-0.2006</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2478</v>
+        <v>-0.6998</v>
       </c>
       <c r="P3" t="n">
-        <v>0.772</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.965</v>
+        <v>-4.0532</v>
       </c>
       <c r="R3" t="n">
         <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5428</v>
+        <v>1.7969</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6155</v>
+        <v>1.3788</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0727</v>
+        <v>0.418</v>
       </c>
       <c r="V3" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.4559</v>
+      </c>
+      <c r="X3" t="n">
         <v>-1.228</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.2859</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-1.5138</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. LINDE GIL</t>
+          <t>T. TAPÉ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8805</v>
+        <v>5.6305</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0411</v>
+        <v>4.9447</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1606</v>
+        <v>0.6857</v>
       </c>
       <c r="G4" t="n">
-        <v>6.1398</v>
+        <v>4.5575</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6375999999999999</v>
+        <v>2.2912</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5023</v>
+        <v>2.2663</v>
       </c>
       <c r="J4" t="n">
-        <v>7.0402</v>
+        <v>4.29</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8381999999999999</v>
+        <v>2.2715</v>
       </c>
       <c r="L4" t="n">
-        <v>6.202</v>
+        <v>2.0185</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9004</v>
+        <v>0.2675</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2006</v>
+        <v>0.0198</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6998</v>
+        <v>0.2478</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.3161</v>
+        <v>0.772</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.0532</v>
+        <v>-0.965</v>
       </c>
       <c r="R4" t="n">
         <v>1.7371</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1712</v>
+        <v>1.5289</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4019</v>
+        <v>1.3339</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2307</v>
+        <v>0.195</v>
       </c>
       <c r="V4" t="n">
-        <v>1.228</v>
+        <v>-1.228</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4559</v>
+        <v>0.2859</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.228</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.7259</v>
+        <v>4.6724</v>
       </c>
       <c r="E5" t="n">
         <v>4.8655</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1395</v>
+        <v>-0.1931</v>
       </c>
       <c r="G5" t="n">
         <v>4.4658</v>
@@ -844,13 +844,13 @@
         <v>0.386</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2023</v>
+        <v>0.1487</v>
       </c>
       <c r="T5" t="n">
         <v>-0.119</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3212</v>
+        <v>0.2677</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3281</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MARTÍN CASTAÑEDA</t>
+          <t>J. TEJERINA TEJEDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.3708</v>
+        <v>3.4973</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4763</v>
+        <v>2.2519</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1055</v>
+        <v>1.2454</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0975</v>
+        <v>0.2862</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1397</v>
+        <v>1.4408</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0421</v>
+        <v>-1.1546</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5792</v>
+        <v>0.9732</v>
       </c>
       <c r="K6" t="n">
-        <v>1.335</v>
+        <v>1.5679</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2442</v>
+        <v>-0.5948</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4817</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1953</v>
+        <v>-0.1272</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2863</v>
+        <v>-0.5598</v>
       </c>
       <c r="P6" t="n">
-        <v>0.193</v>
+        <v>1.3511</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.158</v>
+        <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4662</v>
+        <v>1.86</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2481</v>
+        <v>1.2787</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2181</v>
+        <v>0.5813</v>
       </c>
       <c r="V6" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. TEJERINA TEJEDO</t>
+          <t>M. SOLORZANO COLSA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7576</v>
+        <v>3.4709</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4319</v>
+        <v>1.1336</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3257</v>
+        <v>2.3373</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2862</v>
+        <v>2.7931</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4408</v>
+        <v>1.1116</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1546</v>
+        <v>1.6815</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9732</v>
+        <v>2.0854</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5679</v>
+        <v>0.7916</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5948</v>
+        <v>1.2938</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6870000000000001</v>
+        <v>0.7077</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1272</v>
+        <v>0.32</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5598</v>
+        <v>0.3877</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3511</v>
+        <v>-0.579</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.1231</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1204</v>
+        <v>1.2146</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4587</v>
+        <v>0.8854</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6616</v>
+        <v>0.3291</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2436</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SOLORZANO COLSA</t>
+          <t>A. MARTÍN CASTAÑEDA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2683</v>
+        <v>2.9341</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5734</v>
+        <v>3.0931</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6948</v>
+        <v>-0.159</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7931</v>
+        <v>0.0975</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1116</v>
+        <v>0.1397</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6815</v>
+        <v>-0.0421</v>
       </c>
       <c r="J8" t="n">
-        <v>2.0854</v>
+        <v>1.5792</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7916</v>
+        <v>1.335</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2938</v>
+        <v>0.2442</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7077</v>
+        <v>-1.4817</v>
       </c>
       <c r="N8" t="n">
-        <v>0.32</v>
+        <v>-1.1953</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3877</v>
+        <v>-0.2863</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.579</v>
+        <v>0.193</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1231</v>
+        <v>-0.965</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5441</v>
+        <v>1.158</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0119</v>
+        <v>2.0296</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3252</v>
+        <v>1.865</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3133</v>
+        <v>0.1646</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0422</v>
+        <v>0.614</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2859</v>
+        <v>0.614</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2436</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. VASQUEZ BAUTISTA</t>
+          <t>D. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5004999999999999</v>
+        <v>-0.2696</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8781</v>
+        <v>-3.1077</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3787</v>
+        <v>2.838</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9404</v>
+        <v>-0.2738</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4241</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5162</v>
+        <v>-0.8711</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1259</v>
+        <v>-1.0282</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0038</v>
+        <v>0.1035</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1221</v>
+        <v>-1.1317</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8145</v>
+        <v>0.7544</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4203</v>
+        <v>0.4938</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3941</v>
+        <v>0.2606</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.2811</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.0532</v>
+        <v>-2.8951</v>
       </c>
       <c r="R9" t="n">
         <v>0.772</v>
       </c>
       <c r="S9" t="n">
-        <v>2.7834</v>
+        <v>1.1851</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7054</v>
+        <v>0.5298</v>
       </c>
       <c r="U9" t="n">
-        <v>1.078</v>
+        <v>0.6553</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9421</v>
+        <v>0.9421</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6562</v>
+        <v>0.2859</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2859</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. CARRETERO GARCIA</t>
+          <t>C. HERNÁNDEZ MARTÍN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.456</v>
+        <v>-0.3846</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2673</v>
+        <v>0.0497</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8113</v>
+        <v>-0.4343</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2738</v>
+        <v>-0.2073</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5973000000000001</v>
+        <v>-0.6892</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8711</v>
+        <v>0.482</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0282</v>
+        <v>-0.4206</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1035</v>
+        <v>0.1656</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1317</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7544</v>
+        <v>0.2134</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4938</v>
+        <v>-0.8548</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2606</v>
+        <v>1.0682</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1231</v>
+        <v>0.386</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.8951</v>
+        <v>-0.193</v>
       </c>
       <c r="R10" t="n">
-        <v>0.772</v>
+        <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9987</v>
+        <v>0.6646</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3702</v>
+        <v>0.6633</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6286</v>
+        <v>0.0013</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9421</v>
+        <v>-1.228</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6562</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.495</v>
+        <v>-0.4682</v>
       </c>
       <c r="E11" t="n">
         <v>0.1221</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6171</v>
+        <v>-0.5903</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7059</v>
@@ -1312,13 +1312,13 @@
         <v>0.193</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. HERNÁNDEZ MARTÍN</t>
+          <t>A. VASQUEZ BAUTISTA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6513</v>
+        <v>-0.489</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1099</v>
+        <v>-2.5196</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5414</v>
+        <v>2.0307</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2073</v>
+        <v>1.9404</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6892</v>
+        <v>1.4241</v>
       </c>
       <c r="I12" t="n">
-        <v>0.482</v>
+        <v>0.5162</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4206</v>
+        <v>1.1259</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1656</v>
+        <v>1.0038</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5862000000000001</v>
+        <v>0.1221</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2134</v>
+        <v>0.8145</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8548</v>
+        <v>0.4203</v>
       </c>
       <c r="O12" t="n">
-        <v>1.0682</v>
+        <v>0.3941</v>
       </c>
       <c r="P12" t="n">
-        <v>0.386</v>
+        <v>-3.2811</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.193</v>
+        <v>-4.0532</v>
       </c>
       <c r="R12" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3979</v>
+        <v>1.7939</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5037</v>
+        <v>1.0639</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1058</v>
+        <v>0.73</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.228</v>
+        <v>-0.9421</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.228</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.2795</v>
+        <v>-1.0524</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2118</v>
+        <v>-0.0115</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0677</v>
+        <v>-1.041</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8957000000000001</v>
@@ -1468,13 +1468,13 @@
         <v>0.193</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0178</v>
+        <v>0.2449</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>0.2003</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V13" t="n">
         <v>0.3704</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>31.5557</v>
+        <v>32.4481</v>
       </c>
       <c r="E14" t="n">
-        <v>22.3709</v>
+        <v>23.2631</v>
       </c>
       <c r="F14" t="n">
-        <v>9.184800000000001</v>
+        <v>9.184799999999999</v>
       </c>
       <c r="G14" t="n">
         <v>22.39</v>
       </c>
       <c r="H14" t="n">
-        <v>8.813000000000002</v>
+        <v>8.813000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>13.5771</v>
@@ -1534,7 +1534,7 @@
         <v>-3.6418</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1607999999999998</v>
+        <v>-0.1607999999999999</v>
       </c>
       <c r="P14" t="n">
         <v>-5.7902</v>
@@ -1546,22 +1546,22 @@
         <v>12.5455</v>
       </c>
       <c r="S14" t="n">
-        <v>14.6275</v>
+        <v>15.5199</v>
       </c>
       <c r="T14" t="n">
-        <v>9.855500000000001</v>
+        <v>10.7478</v>
       </c>
       <c r="U14" t="n">
-        <v>4.772</v>
+        <v>4.7719</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3281</v>
+        <v>0.3280999999999997</v>
       </c>
       <c r="W14" t="n">
         <v>4.6585</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.330299999999999</v>
+        <v>-4.3303</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3186</v>
+        <v>1.3718</v>
       </c>
       <c r="E15" t="n">
         <v>4.0806</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.762</v>
+        <v>-2.7088</v>
       </c>
       <c r="G15" t="n">
         <v>1.1571</v>
@@ -1624,13 +1624,13 @@
         <v>2.5091</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1317</v>
+        <v>-2.0785</v>
       </c>
       <c r="T15" t="n">
         <v>-0.4481</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.6836</v>
+        <v>-1.6304</v>
       </c>
       <c r="V15" t="n">
         <v>0.9421</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9866</v>
+        <v>-1.7728</v>
       </c>
       <c r="E18" t="n">
         <v>-0.5641</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4225</v>
+        <v>-1.2087</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7761</v>
@@ -1858,13 +1858,13 @@
         <v>1.158</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0754</v>
+        <v>-0.8616</v>
       </c>
       <c r="T18" t="n">
         <v>-0.5949</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4805</v>
+        <v>-0.2667</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3281</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1957</v>
+        <v>-3.1578</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3047</v>
+        <v>0.5036</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.5004</v>
+        <v>-3.6613</v>
       </c>
       <c r="G19" t="n">
         <v>-2.3436</v>
@@ -1936,13 +1936,13 @@
         <v>2.8951</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4937</v>
+        <v>-1.4558</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4707</v>
+        <v>-0.3304</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9644</v>
+        <v>-1.1254</v>
       </c>
       <c r="V19" t="n">
         <v>1.7997</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5562</v>
+        <v>-3.3893</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8233</v>
+        <v>0.7232</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.3795</v>
+        <v>-4.1125</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1209</v>
@@ -2014,13 +2014,13 @@
         <v>1.7371</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6934</v>
+        <v>-1.5265</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.6077</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1858</v>
+        <v>-0.9188</v>
       </c>
       <c r="V20" t="n">
         <v>-1.5138</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.729</v>
+        <v>-3.7154</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9698</v>
+        <v>-3.1701</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7592</v>
+        <v>-0.5454</v>
       </c>
       <c r="G21" t="n">
         <v>-3.5248</v>
@@ -2092,13 +2092,13 @@
         <v>2.1231</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.8025</v>
+        <v>-1.789</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3437</v>
+        <v>-0.544</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4588</v>
+        <v>-1.245</v>
       </c>
       <c r="V21" t="n">
         <v>1.5983</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.193</v>
+        <v>-4.6126</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5734</v>
+        <v>-2.0727</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6196</v>
+        <v>-2.5399</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4538</v>
@@ -2170,13 +2170,13 @@
         <v>2.8951</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.6777</v>
+        <v>-2.0973</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3537</v>
+        <v>-0.853</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.324</v>
+        <v>-1.2443</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0266</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2479</v>
+        <v>-5.0004</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2421</v>
+        <v>-3.3422</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0058</v>
+        <v>-1.6581</v>
       </c>
       <c r="G23" t="n">
         <v>-5.6115</v>
@@ -2248,13 +2248,13 @@
         <v>2.1231</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5665</v>
+        <v>-1.319</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6411</v>
+        <v>-0.7413</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9254</v>
+        <v>-0.5777</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5693</v>
+        <v>-5.1618</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6177</v>
+        <v>-3.3173</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9516</v>
+        <v>-1.8445</v>
       </c>
       <c r="G24" t="n">
         <v>-3.895</v>
@@ -2326,13 +2326,13 @@
         <v>0.965</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1025</v>
+        <v>-0.695</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7733</v>
+        <v>-0.4729</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3292</v>
+        <v>-0.2221</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5717</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.2514</v>
+        <v>-5.637</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5092</v>
+        <v>-2.1086</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.7422</v>
+        <v>-3.5284</v>
       </c>
       <c r="G25" t="n">
         <v>-3.9044</v>
@@ -2404,13 +2404,13 @@
         <v>1.158</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.0841</v>
+        <v>-1.4697</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5803</v>
+        <v>-0.1798</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.5038</v>
+        <v>-1.2899</v>
       </c>
       <c r="V25" t="n">
         <v>-1.228</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-31.5557</v>
+        <v>-30.2205</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.184900000000001</v>
+        <v>-9.184800000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-22.3708</v>
+        <v>-21.0356</v>
       </c>
       <c r="G26" t="n">
         <v>-22.3902</v>
@@ -2482,13 +2482,13 @@
         <v>18.3356</v>
       </c>
       <c r="S26" t="n">
-        <v>-14.6275</v>
+        <v>-13.2924</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.772</v>
+        <v>-4.7721</v>
       </c>
       <c r="U26" t="n">
-        <v>-9.855499999999999</v>
+        <v>-8.520300000000001</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3280999999999997</v>
